--- a/data/derived_data/5_SBMclustering/Dataset_2/ps_ITS_rare_D2_tax_table.xlsx
+++ b/data/derived_data/5_SBMclustering/Dataset_2/ps_ITS_rare_D2_tax_table.xlsx
@@ -53,10 +53,10 @@
     <t xml:space="preserve">Pichiales</t>
   </si>
   <si>
-    <t xml:space="preserve">Pichiaceae_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pichia_1</t>
+    <t xml:space="preserve">Pichiaceae_1_1_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pichia_1_1_1</t>
   </si>
   <si>
     <t xml:space="preserve">Pichia kluyveri</t>
@@ -68,10 +68,10 @@
     <t xml:space="preserve">Serinales</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_100</t>
+    <t xml:space="preserve">Metschnikowiaceae_100_100_100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_100_100_100</t>
   </si>
   <si>
     <t xml:space="preserve">Metschnikowia rubicola</t>
@@ -86,10 +86,10 @@
     <t xml:space="preserve">Dothideales</t>
   </si>
   <si>
-    <t xml:space="preserve">Dothideaceae_101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dothiora_101</t>
+    <t xml:space="preserve">Dothideaceae_101_101_101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dothiora_101_101_101</t>
   </si>
   <si>
     <t xml:space="preserve">Dothiora prunorum</t>
@@ -104,10 +104,10 @@
     <t xml:space="preserve">Saccharomycetales</t>
   </si>
   <si>
-    <t xml:space="preserve">Phaffomycetaceae_103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wickerhamomyces_103</t>
+    <t xml:space="preserve">Phaffomycetaceae_103_103_103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wickerhamomyces_103_103_103</t>
   </si>
   <si>
     <t xml:space="preserve">Wickerhamomyces pijperi</t>
@@ -119,10 +119,10 @@
     <t xml:space="preserve">Mycosphaerellales</t>
   </si>
   <si>
-    <t xml:space="preserve">Mycosphaerellaceae_108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramularia_108</t>
+    <t xml:space="preserve">Mycosphaerellaceae_108_108_108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramularia_108_108_108</t>
   </si>
   <si>
     <t xml:space="preserve">Ramularia hydrangeae-macrophyllae</t>
@@ -134,16 +134,16 @@
     <t xml:space="preserve">Unknown</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_109_109</t>
+    <t xml:space="preserve">Unknown_109_109_109_109</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_112</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_112</t>
+    <t xml:space="preserve">Metschnikowiaceae_112_112_112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_112_112_112</t>
   </si>
   <si>
     <t xml:space="preserve">Metschnikowia pulcherrima</t>
@@ -152,10 +152,10 @@
     <t xml:space="preserve">Cluster_116</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_116</t>
+    <t xml:space="preserve">Metschnikowiaceae_116_116_116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_116_116_116</t>
   </si>
   <si>
     <t xml:space="preserve">Metschnikowia chrysoperlae</t>
@@ -164,10 +164,10 @@
     <t xml:space="preserve">Cluster_12</t>
   </si>
   <si>
-    <t xml:space="preserve">Pichiaceae_12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pichia_12</t>
+    <t xml:space="preserve">Pichiaceae_12_12_12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pichia_12_12_12</t>
   </si>
   <si>
     <t xml:space="preserve">Pichia nakasei</t>
@@ -185,28 +185,28 @@
     <t xml:space="preserve">Tremellales</t>
   </si>
   <si>
-    <t xml:space="preserve">Bulleribasidiaceae_123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vishniacozyma_123</t>
+    <t xml:space="preserve">Bulleribasidiaceae_123_123_123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vishniacozyma_123_123_123</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_127</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_127</t>
+    <t xml:space="preserve">Metschnikowiaceae_127_127_127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_127_127_127</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_13</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_13</t>
+    <t xml:space="preserve">Metschnikowiaceae_13_13_13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_13_13_13</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_134</t>
@@ -218,10 +218,10 @@
     <t xml:space="preserve">Taphrinales</t>
   </si>
   <si>
-    <t xml:space="preserve">Taphrinaceae_134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taphrina_134</t>
+    <t xml:space="preserve">Taphrinaceae_134_134_134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taphrina_134_134_134</t>
   </si>
   <si>
     <t xml:space="preserve">Taphrina wiesneri</t>
@@ -233,25 +233,25 @@
     <t xml:space="preserve">Cladosporiales</t>
   </si>
   <si>
-    <t xml:space="preserve">Cladosporiaceae_14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cladosporium_14</t>
+    <t xml:space="preserve">Cladosporiaceae_14_14_14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cladosporium_14_14_14</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_15</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_15</t>
+    <t xml:space="preserve">Metschnikowiaceae_15_15_15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_15_15_15</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_158</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_158_158</t>
+    <t xml:space="preserve">Unknown_158_158_158_158</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_159</t>
@@ -260,10 +260,10 @@
     <t xml:space="preserve">Pleosporales</t>
   </si>
   <si>
-    <t xml:space="preserve">Pleosporaceae_159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stemphylium_159</t>
+    <t xml:space="preserve">Pleosporaceae_159_159_159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stemphylium_159_159_159</t>
   </si>
   <si>
     <t xml:space="preserve">Stemphylium globuliferum</t>
@@ -272,10 +272,10 @@
     <t xml:space="preserve">Cluster_16</t>
   </si>
   <si>
-    <t xml:space="preserve">Cladosporiaceae_16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cladosporium_16</t>
+    <t xml:space="preserve">Cladosporiaceae_16_16_16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cladosporium_16_16_16</t>
   </si>
   <si>
     <t xml:space="preserve">Cladosporium herbarum</t>
@@ -284,25 +284,25 @@
     <t xml:space="preserve">Cluster_163</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_163_163</t>
+    <t xml:space="preserve">Unknown_163_163_163_163</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_165</t>
   </si>
   <si>
-    <t xml:space="preserve">Cladosporiaceae_165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unknown_165_165</t>
+    <t xml:space="preserve">Cladosporiaceae_165_165_165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown_165_165_165_165</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_166</t>
   </si>
   <si>
-    <t xml:space="preserve">Bulleribasidiaceae_166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vishniacozyma_166</t>
+    <t xml:space="preserve">Bulleribasidiaceae_166_166_166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vishniacozyma_166_166_166</t>
   </si>
   <si>
     <t xml:space="preserve">Vishniacozyma victoriae</t>
@@ -311,19 +311,19 @@
     <t xml:space="preserve">Cluster_17</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_17</t>
+    <t xml:space="preserve">Metschnikowiaceae_17_17_17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_17_17_17</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_174</t>
   </si>
   <si>
-    <t xml:space="preserve">Cladosporiaceae_174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rachicladosporium_174</t>
+    <t xml:space="preserve">Cladosporiaceae_174_174_174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rachicladosporium_174_174_174</t>
   </si>
   <si>
     <t xml:space="preserve">Rachicladosporium cboliae</t>
@@ -332,25 +332,25 @@
     <t xml:space="preserve">Cluster_176</t>
   </si>
   <si>
-    <t xml:space="preserve">Pleosporaceae_176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unknown_176_176</t>
+    <t xml:space="preserve">Pleosporaceae_176_176_176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown_176_176_176_176</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_179</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_179_179</t>
+    <t xml:space="preserve">Unknown_179_179_179_179</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_18</t>
   </si>
   <si>
-    <t xml:space="preserve">Saccharomycodaceae_18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hanseniaspora_18</t>
+    <t xml:space="preserve">Saccharomycodaceae_18_18_18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hanseniaspora_18_18_18</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_180</t>
@@ -359,13 +359,13 @@
     <t xml:space="preserve">Microbotryomycetes</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_180_180</t>
+    <t xml:space="preserve">Unknown_180_180_180_180</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_182</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_182_182</t>
+    <t xml:space="preserve">Unknown_182_182_182_182</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_187</t>
@@ -377,10 +377,10 @@
     <t xml:space="preserve">Eurotiales</t>
   </si>
   <si>
-    <t xml:space="preserve">Aspergillaceae_187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penicillium_187</t>
+    <t xml:space="preserve">Aspergillaceae_187_187_187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penicillium_187_187_187</t>
   </si>
   <si>
     <t xml:space="preserve">Penicillium bialowiezense</t>
@@ -389,19 +389,19 @@
     <t xml:space="preserve">Cluster_188</t>
   </si>
   <si>
-    <t xml:space="preserve">Taphrinaceae_188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taphrina_188</t>
+    <t xml:space="preserve">Taphrinaceae_188_188_188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taphrina_188_188_188</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_194</t>
   </si>
   <si>
-    <t xml:space="preserve">Trichomonascaceae_194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Starmerella_194</t>
+    <t xml:space="preserve">Trichomonascaceae_194_194_194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starmerella_194_194_194</t>
   </si>
   <si>
     <t xml:space="preserve">Starmerella stellata</t>
@@ -410,19 +410,19 @@
     <t xml:space="preserve">Cluster_2</t>
   </si>
   <si>
-    <t xml:space="preserve">Pichiaceae_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pichia_2</t>
+    <t xml:space="preserve">Pichiaceae_2_2_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pichia_2_2_2</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_20</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_20</t>
+    <t xml:space="preserve">Metschnikowiaceae_20_20_20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_20_20_20</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_209</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">Helotiales</t>
   </si>
   <si>
-    <t xml:space="preserve">Lachnaceae_209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lachnum_209</t>
+    <t xml:space="preserve">Lachnaceae_209_209_209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lachnum_209_209_209</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_214</t>
   </si>
   <si>
-    <t xml:space="preserve">Bulleribasidiaceae_214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vishniacozyma_214</t>
+    <t xml:space="preserve">Bulleribasidiaceae_214_214_214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vishniacozyma_214_214_214</t>
   </si>
   <si>
     <t xml:space="preserve">Vishniacozyma heimaeyensis</t>
@@ -461,25 +461,25 @@
     <t xml:space="preserve">Microstromatales</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_215_215</t>
+    <t xml:space="preserve">Unknown_215_215_215_215</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_22</t>
   </si>
   <si>
-    <t xml:space="preserve">Pleosporaceae_22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alternaria_22</t>
+    <t xml:space="preserve">Pleosporaceae_22_22_22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alternaria_22_22_22</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_223</t>
   </si>
   <si>
-    <t xml:space="preserve">Taphrinaceae_223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taphrina_223</t>
+    <t xml:space="preserve">Taphrinaceae_223_223_223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taphrina_223_223_223</t>
   </si>
   <si>
     <t xml:space="preserve">Taphrina carpini</t>
@@ -488,34 +488,34 @@
     <t xml:space="preserve">Cluster_231</t>
   </si>
   <si>
-    <t xml:space="preserve">Bulleribasidiaceae_231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vishniacozyma_231</t>
+    <t xml:space="preserve">Bulleribasidiaceae_231_231_231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vishniacozyma_231_231_231</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_240</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_240_240</t>
+    <t xml:space="preserve">Unknown_240_240_240_240</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_242</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_242</t>
+    <t xml:space="preserve">Metschnikowiaceae_242_242_242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_242_242_242</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_245</t>
   </si>
   <si>
-    <t xml:space="preserve">Cladosporiaceae_245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cladosporium_245</t>
+    <t xml:space="preserve">Cladosporiaceae_245_245_245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cladosporium_245_245_245</t>
   </si>
   <si>
     <t xml:space="preserve">Cladosporium entadae</t>
@@ -524,10 +524,10 @@
     <t xml:space="preserve">Cluster_249</t>
   </si>
   <si>
-    <t xml:space="preserve">Bulleribasidiaceae_249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vishniacozyma_249</t>
+    <t xml:space="preserve">Bulleribasidiaceae_249_249_249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vishniacozyma_249_249_249</t>
   </si>
   <si>
     <t xml:space="preserve">Vishniacozyma tephrensis</t>
@@ -536,64 +536,64 @@
     <t xml:space="preserve">Cluster_257</t>
   </si>
   <si>
-    <t xml:space="preserve">Bulleribasidiaceae_257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dioszegia_257</t>
+    <t xml:space="preserve">Bulleribasidiaceae_257_257_257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dioszegia_257_257_257</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_259</t>
   </si>
   <si>
-    <t xml:space="preserve">Pleosporaceae_259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alternaria_259</t>
+    <t xml:space="preserve">Pleosporaceae_259_259_259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alternaria_259_259_259</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_267</t>
   </si>
   <si>
-    <t xml:space="preserve">Cladosporiaceae_267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cladosporium_267</t>
+    <t xml:space="preserve">Cladosporiaceae_267_267_267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cladosporium_267_267_267</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_27</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_27</t>
+    <t xml:space="preserve">Metschnikowiaceae_27_27_27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_27_27_27</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_272</t>
   </si>
   <si>
-    <t xml:space="preserve">Mycosphaerellaceae_272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramularia_272</t>
+    <t xml:space="preserve">Mycosphaerellaceae_272_272_272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramularia_272_272_272</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_274</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_274</t>
+    <t xml:space="preserve">Metschnikowiaceae_274_274_274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_274_274_274</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_28</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_28</t>
+    <t xml:space="preserve">Metschnikowiaceae_28_28_28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_28_28_28</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_281</t>
@@ -602,10 +602,10 @@
     <t xml:space="preserve">Cystobasidiomycetes</t>
   </si>
   <si>
-    <t xml:space="preserve">Symmetrosporaceae_281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unknown_281_281</t>
+    <t xml:space="preserve">Symmetrosporaceae_281_281_281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown_281_281_281_281</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_289</t>
@@ -614,10 +614,10 @@
     <t xml:space="preserve">Sporidiobolales</t>
   </si>
   <si>
-    <t xml:space="preserve">Sporidiobolaceae_289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sporobolomyces_289</t>
+    <t xml:space="preserve">Sporidiobolaceae_289_289_289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sporobolomyces_289_289_289</t>
   </si>
   <si>
     <t xml:space="preserve">Sporobolomyces reniformis</t>
@@ -626,19 +626,19 @@
     <t xml:space="preserve">Cluster_29</t>
   </si>
   <si>
-    <t xml:space="preserve">Phaffomycetaceae_29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wickerhamomyces_29</t>
+    <t xml:space="preserve">Phaffomycetaceae_29_29_29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wickerhamomyces_29_29_29</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_295</t>
   </si>
   <si>
-    <t xml:space="preserve">Cladosporiaceae_295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cladosporium_295</t>
+    <t xml:space="preserve">Cladosporiaceae_295_295_295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cladosporium_295_295_295</t>
   </si>
   <si>
     <t xml:space="preserve">Cladosporium succulentum</t>
@@ -647,10 +647,10 @@
     <t xml:space="preserve">Cluster_3</t>
   </si>
   <si>
-    <t xml:space="preserve">Pichiaceae_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pichia_3</t>
+    <t xml:space="preserve">Pichiaceae_3_3_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pichia_3_3_3</t>
   </si>
   <si>
     <t xml:space="preserve">Pichia terricola</t>
@@ -659,10 +659,10 @@
     <t xml:space="preserve">Cluster_30</t>
   </si>
   <si>
-    <t xml:space="preserve">Aspergillaceae_30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penicillium_30</t>
+    <t xml:space="preserve">Aspergillaceae_30_30_30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penicillium_30_30_30</t>
   </si>
   <si>
     <t xml:space="preserve">Penicillium brevicompactum</t>
@@ -671,10 +671,10 @@
     <t xml:space="preserve">Cluster_300</t>
   </si>
   <si>
-    <t xml:space="preserve">Sporidiobolaceae_300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sporobolomyces_300</t>
+    <t xml:space="preserve">Sporidiobolaceae_300_300_300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sporobolomyces_300_300_300</t>
   </si>
   <si>
     <t xml:space="preserve">Sporobolomyces roseus</t>
@@ -683,10 +683,10 @@
     <t xml:space="preserve">Cluster_31</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_31</t>
+    <t xml:space="preserve">Metschnikowiaceae_31_31_31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_31_31_31</t>
   </si>
   <si>
     <t xml:space="preserve">Metschnikowia leonuri</t>
@@ -695,46 +695,46 @@
     <t xml:space="preserve">Cluster_317</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_317_317</t>
+    <t xml:space="preserve">Unknown_317_317_317_317</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_32</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_32</t>
+    <t xml:space="preserve">Metschnikowiaceae_32_32_32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_32_32_32</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_33</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_33</t>
+    <t xml:space="preserve">Metschnikowiaceae_33_33_33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_33_33_33</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_34</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_34_34</t>
+    <t xml:space="preserve">Unknown_34_34_34_34</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_340</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_340_340</t>
+    <t xml:space="preserve">Unknown_340_340_340_340</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_341</t>
   </si>
   <si>
-    <t xml:space="preserve">Mycosphaerellaceae_341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramularia_341</t>
+    <t xml:space="preserve">Mycosphaerellaceae_341_341_341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramularia_341_341_341</t>
   </si>
   <si>
     <t xml:space="preserve">Ramularia eucalypti</t>
@@ -743,76 +743,76 @@
     <t xml:space="preserve">Cluster_35</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_35</t>
+    <t xml:space="preserve">Metschnikowiaceae_35_35_35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_35_35_35</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_37</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_37</t>
+    <t xml:space="preserve">Metschnikowiaceae_37_37_37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_37_37_37</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_371</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_371_371</t>
+    <t xml:space="preserve">Unknown_371_371_371_371</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_379</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_379</t>
+    <t xml:space="preserve">Metschnikowiaceae_379_379_379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_379_379_379</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_38</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_38</t>
+    <t xml:space="preserve">Metschnikowiaceae_38_38_38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_38_38_38</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_39</t>
   </si>
   <si>
-    <t xml:space="preserve">Phaffomycetaceae_39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wickerhamomyces_39</t>
+    <t xml:space="preserve">Phaffomycetaceae_39_39_39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wickerhamomyces_39_39_39</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_391</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_391_391</t>
+    <t xml:space="preserve">Unknown_391_391_391_391</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_4</t>
   </si>
   <si>
-    <t xml:space="preserve">Sclerotiniaceae_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unknown_4_4</t>
+    <t xml:space="preserve">Sclerotiniaceae_4_4_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown_4_4_4_4</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_41</t>
   </si>
   <si>
-    <t xml:space="preserve">Erysiphaceae_41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Podosphaera_41</t>
+    <t xml:space="preserve">Erysiphaceae_41_41_41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Podosphaera_41_41_41</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_422</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">Mucorales</t>
   </si>
   <si>
-    <t xml:space="preserve">Mucoraceae_422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mucor_422</t>
+    <t xml:space="preserve">Mucoraceae_422_422_422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mucor_422_422_422</t>
   </si>
   <si>
     <t xml:space="preserve">Mucor circinelloides</t>
@@ -839,25 +839,25 @@
     <t xml:space="preserve">Cluster_423</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_423_423</t>
+    <t xml:space="preserve">Unknown_423_423_423_423</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_44</t>
   </si>
   <si>
-    <t xml:space="preserve">Phaffomycetaceae_44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wickerhamomyces_44</t>
+    <t xml:space="preserve">Phaffomycetaceae_44_44_44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wickerhamomyces_44_44_44</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_46</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_46</t>
+    <t xml:space="preserve">Metschnikowiaceae_46_46_46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_46_46_46</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_49</t>
@@ -866,10 +866,10 @@
     <t xml:space="preserve">Filobasidiales</t>
   </si>
   <si>
-    <t xml:space="preserve">Filobasidiaceae_49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filobasidium_49</t>
+    <t xml:space="preserve">Filobasidiaceae_49_49_49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filobasidium_49_49_49</t>
   </si>
   <si>
     <t xml:space="preserve">Filobasidium wieringae</t>
@@ -878,112 +878,112 @@
     <t xml:space="preserve">Cluster_5</t>
   </si>
   <si>
-    <t xml:space="preserve">Cladosporiaceae_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cladosporium_5</t>
+    <t xml:space="preserve">Cladosporiaceae_5_5_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cladosporium_5_5_5</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_51</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_51_51</t>
+    <t xml:space="preserve">Unknown_51_51_51_51</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_53</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_53</t>
+    <t xml:space="preserve">Metschnikowiaceae_53_53_53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_53_53_53</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_540</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_540_540</t>
+    <t xml:space="preserve">Unknown_540_540_540_540</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_55</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_55</t>
+    <t xml:space="preserve">Metschnikowiaceae_55_55_55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_55_55_55</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_57</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_57</t>
+    <t xml:space="preserve">Metschnikowiaceae_57_57_57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_57_57_57</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_576</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_576_576</t>
+    <t xml:space="preserve">Unknown_576_576_576_576</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_58</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_58_58</t>
+    <t xml:space="preserve">Unknown_58_58_58_58</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_59</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_59</t>
+    <t xml:space="preserve">Metschnikowiaceae_59_59_59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_59_59_59</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_6</t>
   </si>
   <si>
-    <t xml:space="preserve">Sclerotiniaceae_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unknown_6_6</t>
+    <t xml:space="preserve">Sclerotiniaceae_6_6_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown_6_6_6_6</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_615</t>
   </si>
   <si>
-    <t xml:space="preserve">Ploettnerulaceae_615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cadophora_615</t>
+    <t xml:space="preserve">Ploettnerulaceae_615_615_615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cadophora_615_615_615</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_64</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_64</t>
+    <t xml:space="preserve">Metschnikowiaceae_64_64_64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_64_64_64</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_66</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_66_66</t>
+    <t xml:space="preserve">Unknown_66_66_66_66</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_67</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_67</t>
+    <t xml:space="preserve">Metschnikowiaceae_67_67_67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_67_67_67</t>
   </si>
   <si>
     <t xml:space="preserve">Metschnikowia vanudenii</t>
@@ -992,46 +992,46 @@
     <t xml:space="preserve">Cluster_68</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_68_68</t>
+    <t xml:space="preserve">Unknown_68_68_68_68</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_7</t>
   </si>
   <si>
-    <t xml:space="preserve">Saccharomycodaceae_7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hanseniaspora_7</t>
+    <t xml:space="preserve">Saccharomycodaceae_7_7_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hanseniaspora_7_7_7</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_72</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_72_72</t>
+    <t xml:space="preserve">Unknown_72_72_72_72</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_73</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_73</t>
+    <t xml:space="preserve">Metschnikowiaceae_73_73_73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_73_73_73</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_744</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_744_744</t>
+    <t xml:space="preserve">Unknown_744_744_744_744</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_769</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_769</t>
+    <t xml:space="preserve">Metschnikowiaceae_769_769_769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_769_769_769</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_78</t>
@@ -1040,10 +1040,10 @@
     <t xml:space="preserve">Ascoideales</t>
   </si>
   <si>
-    <t xml:space="preserve">Saccharomycopsidaceae_78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saccharomycopsis_78</t>
+    <t xml:space="preserve">Saccharomycopsidaceae_78_78_78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saccharomycopsis_78_78_78</t>
   </si>
   <si>
     <t xml:space="preserve">Saccharomycopsis crataegensis</t>
@@ -1052,10 +1052,10 @@
     <t xml:space="preserve">Cluster_8</t>
   </si>
   <si>
-    <t xml:space="preserve">Saccotheciaceae_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aureobasidium_8</t>
+    <t xml:space="preserve">Saccotheciaceae_8_8_8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aureobasidium_8_8_8</t>
   </si>
   <si>
     <t xml:space="preserve">Aureobasidium pullulans</t>
@@ -1064,16 +1064,16 @@
     <t xml:space="preserve">Cluster_81</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_81_81</t>
+    <t xml:space="preserve">Unknown_81_81_81_81</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_85</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_85</t>
+    <t xml:space="preserve">Metschnikowiaceae_85_85_85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_85_85_85</t>
   </si>
   <si>
     <t xml:space="preserve">Metschnikowia gruessii</t>
@@ -1082,55 +1082,55 @@
     <t xml:space="preserve">Cluster_87</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_87_87</t>
+    <t xml:space="preserve">Unknown_87_87_87_87</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_89</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_89_89</t>
+    <t xml:space="preserve">Unknown_89_89_89_89</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_9</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_9</t>
+    <t xml:space="preserve">Metschnikowiaceae_9_9_9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_9_9_9</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_92</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_92</t>
+    <t xml:space="preserve">Metschnikowiaceae_92_92_92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_92_92_92</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_95</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_95_95</t>
+    <t xml:space="preserve">Unknown_95_95_95_95</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_96</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_96</t>
+    <t xml:space="preserve">Metschnikowiaceae_96_96_96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia_96_96_96</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_98</t>
   </si>
   <si>
-    <t xml:space="preserve">Cladosporiaceae_98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cladosporium_98</t>
+    <t xml:space="preserve">Cladosporiaceae_98_98_98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cladosporium_98_98_98</t>
   </si>
 </sst>
 </file>

--- a/data/derived_data/5_SBMclustering/Dataset_2/ps_ITS_rare_D2_tax_table.xlsx
+++ b/data/derived_data/5_SBMclustering/Dataset_2/ps_ITS_rare_D2_tax_table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="255">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -53,10 +53,10 @@
     <t xml:space="preserve">Pichiales</t>
   </si>
   <si>
-    <t xml:space="preserve">Pichiaceae_1_1_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pichia_1_1_1</t>
+    <t xml:space="preserve">Pichiaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pichia</t>
   </si>
   <si>
     <t xml:space="preserve">Pichia kluyveri</t>
@@ -68,10 +68,10 @@
     <t xml:space="preserve">Serinales</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_100_100_100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_100_100_100</t>
+    <t xml:space="preserve">Metschnikowiaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metschnikowia</t>
   </si>
   <si>
     <t xml:space="preserve">Metschnikowia rubicola</t>
@@ -86,10 +86,10 @@
     <t xml:space="preserve">Dothideales</t>
   </si>
   <si>
-    <t xml:space="preserve">Dothideaceae_101_101_101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dothiora_101_101_101</t>
+    <t xml:space="preserve">Dothideaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dothiora</t>
   </si>
   <si>
     <t xml:space="preserve">Dothiora prunorum</t>
@@ -104,10 +104,10 @@
     <t xml:space="preserve">Saccharomycetales</t>
   </si>
   <si>
-    <t xml:space="preserve">Phaffomycetaceae_103_103_103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wickerhamomyces_103_103_103</t>
+    <t xml:space="preserve">Phaffomycetaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wickerhamomyces</t>
   </si>
   <si>
     <t xml:space="preserve">Wickerhamomyces pijperi</t>
@@ -119,10 +119,10 @@
     <t xml:space="preserve">Mycosphaerellales</t>
   </si>
   <si>
-    <t xml:space="preserve">Mycosphaerellaceae_108_108_108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramularia_108_108_108</t>
+    <t xml:space="preserve">Mycosphaerellaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramularia</t>
   </si>
   <si>
     <t xml:space="preserve">Ramularia hydrangeae-macrophyllae</t>
@@ -134,42 +134,24 @@
     <t xml:space="preserve">Unknown</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_109_109_109_109</t>
+    <t xml:space="preserve">Unknown_109</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_112</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_112_112_112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_112_112_112</t>
-  </si>
-  <si>
     <t xml:space="preserve">Metschnikowia pulcherrima</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_116</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_116_116_116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_116_116_116</t>
-  </si>
-  <si>
     <t xml:space="preserve">Metschnikowia chrysoperlae</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_12</t>
   </si>
   <si>
-    <t xml:space="preserve">Pichiaceae_12_12_12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pichia_12_12_12</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pichia nakasei</t>
   </si>
   <si>
@@ -185,30 +167,18 @@
     <t xml:space="preserve">Tremellales</t>
   </si>
   <si>
-    <t xml:space="preserve">Bulleribasidiaceae_123_123_123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vishniacozyma_123_123_123</t>
+    <t xml:space="preserve">Bulleribasidiaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vishniacozyma</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_127</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_127_127_127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_127_127_127</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_13</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_13_13_13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_13_13_13</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_134</t>
   </si>
   <si>
@@ -218,10 +188,10 @@
     <t xml:space="preserve">Taphrinales</t>
   </si>
   <si>
-    <t xml:space="preserve">Taphrinaceae_134_134_134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taphrina_134_134_134</t>
+    <t xml:space="preserve">Taphrinaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taphrina</t>
   </si>
   <si>
     <t xml:space="preserve">Taphrina wiesneri</t>
@@ -233,25 +203,19 @@
     <t xml:space="preserve">Cladosporiales</t>
   </si>
   <si>
-    <t xml:space="preserve">Cladosporiaceae_14_14_14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cladosporium_14_14_14</t>
+    <t xml:space="preserve">Cladosporiaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cladosporium</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_15</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_15_15_15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_15_15_15</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_158</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_158_158_158_158</t>
+    <t xml:space="preserve">Unknown_158</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_159</t>
@@ -260,10 +224,10 @@
     <t xml:space="preserve">Pleosporales</t>
   </si>
   <si>
-    <t xml:space="preserve">Pleosporaceae_159_159_159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stemphylium_159_159_159</t>
+    <t xml:space="preserve">Pleosporaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stemphylium</t>
   </si>
   <si>
     <t xml:space="preserve">Stemphylium globuliferum</t>
@@ -272,58 +236,34 @@
     <t xml:space="preserve">Cluster_16</t>
   </si>
   <si>
-    <t xml:space="preserve">Cladosporiaceae_16_16_16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cladosporium_16_16_16</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cladosporium herbarum</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_163</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_163_163_163_163</t>
+    <t xml:space="preserve">Unknown_163</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_165</t>
   </si>
   <si>
-    <t xml:space="preserve">Cladosporiaceae_165_165_165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unknown_165_165_165_165</t>
+    <t xml:space="preserve">Unknown_165</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_166</t>
   </si>
   <si>
-    <t xml:space="preserve">Bulleribasidiaceae_166_166_166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vishniacozyma_166_166_166</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vishniacozyma victoriae</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_17</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_17_17_17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_17_17_17</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_174</t>
   </si>
   <si>
-    <t xml:space="preserve">Cladosporiaceae_174_174_174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rachicladosporium_174_174_174</t>
+    <t xml:space="preserve">Rachicladosporium</t>
   </si>
   <si>
     <t xml:space="preserve">Rachicladosporium cboliae</t>
@@ -332,25 +272,22 @@
     <t xml:space="preserve">Cluster_176</t>
   </si>
   <si>
-    <t xml:space="preserve">Pleosporaceae_176_176_176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unknown_176_176_176_176</t>
+    <t xml:space="preserve">Unknown_176</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_179</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_179_179_179_179</t>
+    <t xml:space="preserve">Unknown_179</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_18</t>
   </si>
   <si>
-    <t xml:space="preserve">Saccharomycodaceae_18_18_18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hanseniaspora_18_18_18</t>
+    <t xml:space="preserve">Saccharomycodaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hanseniaspora</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_180</t>
@@ -359,13 +296,13 @@
     <t xml:space="preserve">Microbotryomycetes</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_180_180_180_180</t>
+    <t xml:space="preserve">Unknown_180</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_182</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_182_182_182_182</t>
+    <t xml:space="preserve">Unknown_182</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_187</t>
@@ -377,10 +314,10 @@
     <t xml:space="preserve">Eurotiales</t>
   </si>
   <si>
-    <t xml:space="preserve">Aspergillaceae_187_187_187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penicillium_187_187_187</t>
+    <t xml:space="preserve">Aspergillaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penicillium</t>
   </si>
   <si>
     <t xml:space="preserve">Penicillium bialowiezense</t>
@@ -389,19 +326,13 @@
     <t xml:space="preserve">Cluster_188</t>
   </si>
   <si>
-    <t xml:space="preserve">Taphrinaceae_188_188_188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taphrina_188_188_188</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_194</t>
   </si>
   <si>
-    <t xml:space="preserve">Trichomonascaceae_194_194_194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Starmerella_194_194_194</t>
+    <t xml:space="preserve">Trichomonascaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starmerella</t>
   </si>
   <si>
     <t xml:space="preserve">Starmerella stellata</t>
@@ -410,21 +341,9 @@
     <t xml:space="preserve">Cluster_2</t>
   </si>
   <si>
-    <t xml:space="preserve">Pichiaceae_2_2_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pichia_2_2_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_20</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_20_20_20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_20_20_20</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_209</t>
   </si>
   <si>
@@ -434,21 +353,15 @@
     <t xml:space="preserve">Helotiales</t>
   </si>
   <si>
-    <t xml:space="preserve">Lachnaceae_209_209_209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lachnum_209_209_209</t>
+    <t xml:space="preserve">Lachnaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lachnum</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_214</t>
   </si>
   <si>
-    <t xml:space="preserve">Bulleribasidiaceae_214_214_214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vishniacozyma_214_214_214</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vishniacozyma heimaeyensis</t>
   </si>
   <si>
@@ -461,151 +374,94 @@
     <t xml:space="preserve">Microstromatales</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_215_215_215_215</t>
+    <t xml:space="preserve">Unknown_215</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_22</t>
   </si>
   <si>
-    <t xml:space="preserve">Pleosporaceae_22_22_22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alternaria_22_22_22</t>
+    <t xml:space="preserve">Alternaria</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_223</t>
   </si>
   <si>
-    <t xml:space="preserve">Taphrinaceae_223_223_223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taphrina_223_223_223</t>
-  </si>
-  <si>
     <t xml:space="preserve">Taphrina carpini</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_231</t>
   </si>
   <si>
-    <t xml:space="preserve">Bulleribasidiaceae_231_231_231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vishniacozyma_231_231_231</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_240</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_240_240_240_240</t>
+    <t xml:space="preserve">Viridiplantae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streptophyta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magnoliopsida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rubus</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_242</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_242_242_242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_242_242_242</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_245</t>
   </si>
   <si>
-    <t xml:space="preserve">Cladosporiaceae_245_245_245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cladosporium_245_245_245</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cladosporium entadae</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_249</t>
   </si>
   <si>
-    <t xml:space="preserve">Bulleribasidiaceae_249_249_249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vishniacozyma_249_249_249</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vishniacozyma tephrensis</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_257</t>
   </si>
   <si>
-    <t xml:space="preserve">Bulleribasidiaceae_257_257_257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dioszegia_257_257_257</t>
+    <t xml:space="preserve">Dioszegia</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_259</t>
   </si>
   <si>
-    <t xml:space="preserve">Pleosporaceae_259_259_259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alternaria_259_259_259</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_267</t>
   </si>
   <si>
-    <t xml:space="preserve">Cladosporiaceae_267_267_267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cladosporium_267_267_267</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_27</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_27_27_27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_27_27_27</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_272</t>
   </si>
   <si>
-    <t xml:space="preserve">Mycosphaerellaceae_272_272_272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramularia_272_272_272</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_274</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_274_274_274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_274_274_274</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_28</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_28_28_28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_28_28_28</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_281</t>
   </si>
   <si>
     <t xml:space="preserve">Cystobasidiomycetes</t>
   </si>
   <si>
-    <t xml:space="preserve">Symmetrosporaceae_281_281_281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unknown_281_281_281_281</t>
+    <t xml:space="preserve">Symmetrosporaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown_281</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_289</t>
@@ -614,10 +470,10 @@
     <t xml:space="preserve">Sporidiobolales</t>
   </si>
   <si>
-    <t xml:space="preserve">Sporidiobolaceae_289_289_289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sporobolomyces_289_289_289</t>
+    <t xml:space="preserve">Sporidiobolaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sporobolomyces</t>
   </si>
   <si>
     <t xml:space="preserve">Sporobolomyces reniformis</t>
@@ -626,193 +482,106 @@
     <t xml:space="preserve">Cluster_29</t>
   </si>
   <si>
-    <t xml:space="preserve">Phaffomycetaceae_29_29_29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wickerhamomyces_29_29_29</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_295</t>
   </si>
   <si>
-    <t xml:space="preserve">Cladosporiaceae_295_295_295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cladosporium_295_295_295</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cladosporium succulentum</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_3</t>
   </si>
   <si>
-    <t xml:space="preserve">Pichiaceae_3_3_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pichia_3_3_3</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pichia terricola</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_30</t>
   </si>
   <si>
-    <t xml:space="preserve">Aspergillaceae_30_30_30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penicillium_30_30_30</t>
-  </si>
-  <si>
     <t xml:space="preserve">Penicillium brevicompactum</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_300</t>
   </si>
   <si>
-    <t xml:space="preserve">Sporidiobolaceae_300_300_300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sporobolomyces_300_300_300</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sporobolomyces roseus</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_31</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_31_31_31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_31_31_31</t>
-  </si>
-  <si>
     <t xml:space="preserve">Metschnikowia leonuri</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_317</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_317_317_317_317</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_32</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_32_32_32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_32_32_32</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_33</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_33_33_33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_33_33_33</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_34</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_34_34_34_34</t>
+    <t xml:space="preserve">Unknown_34</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_340</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_340_340_340_340</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_341</t>
   </si>
   <si>
-    <t xml:space="preserve">Mycosphaerellaceae_341_341_341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramularia_341_341_341</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ramularia eucalypti</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_35</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_35_35_35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_35_35_35</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_37</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_37_37_37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_37_37_37</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_371</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_371_371_371_371</t>
+    <t xml:space="preserve">Prunus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avium</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_379</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_379_379_379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_379_379_379</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_38</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_38_38_38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_38_38_38</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_39</t>
   </si>
   <si>
-    <t xml:space="preserve">Phaffomycetaceae_39_39_39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wickerhamomyces_39_39_39</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_391</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_391_391_391_391</t>
+    <t xml:space="preserve">Unknown_391</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_4</t>
   </si>
   <si>
-    <t xml:space="preserve">Sclerotiniaceae_4_4_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unknown_4_4_4_4</t>
+    <t xml:space="preserve">Sclerotiniaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown_4</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_41</t>
   </si>
   <si>
-    <t xml:space="preserve">Erysiphaceae_41_41_41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Podosphaera_41_41_41</t>
+    <t xml:space="preserve">Erysiphaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Podosphaera</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_422</t>
@@ -827,10 +596,10 @@
     <t xml:space="preserve">Mucorales</t>
   </si>
   <si>
-    <t xml:space="preserve">Mucoraceae_422_422_422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mucor_422_422_422</t>
+    <t xml:space="preserve">Mucoraceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mucor</t>
   </si>
   <si>
     <t xml:space="preserve">Mucor circinelloides</t>
@@ -839,37 +608,25 @@
     <t xml:space="preserve">Cluster_423</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_423_423_423_423</t>
+    <t xml:space="preserve">pulcherrima</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_44</t>
   </si>
   <si>
-    <t xml:space="preserve">Phaffomycetaceae_44_44_44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wickerhamomyces_44_44_44</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_46</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_46_46_46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_46_46_46</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_49</t>
   </si>
   <si>
     <t xml:space="preserve">Filobasidiales</t>
   </si>
   <si>
-    <t xml:space="preserve">Filobasidiaceae_49_49_49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filobasidium_49_49_49</t>
+    <t xml:space="preserve">Filobasidiaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filobasidium</t>
   </si>
   <si>
     <t xml:space="preserve">Filobasidium wieringae</t>
@@ -878,172 +635,100 @@
     <t xml:space="preserve">Cluster_5</t>
   </si>
   <si>
-    <t xml:space="preserve">Cladosporiaceae_5_5_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cladosporium_5_5_5</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_51</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_51_51_51_51</t>
+    <t xml:space="preserve">Unknown_51</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_53</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_53_53_53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_53_53_53</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_540</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_540_540_540_540</t>
+    <t xml:space="preserve">Unknown_540</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_55</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_55_55_55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_55_55_55</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_57</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_57_57_57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_57_57_57</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_576</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_576_576_576_576</t>
+    <t xml:space="preserve">sulcatus</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_58</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_58_58_58_58</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_59</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_59_59_59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_59_59_59</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_6</t>
   </si>
   <si>
-    <t xml:space="preserve">Sclerotiniaceae_6_6_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unknown_6_6_6_6</t>
+    <t xml:space="preserve">Unknown_6</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_615</t>
   </si>
   <si>
-    <t xml:space="preserve">Ploettnerulaceae_615_615_615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cadophora_615_615_615</t>
+    <t xml:space="preserve">Ploettnerulaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cadophora</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_64</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_64_64_64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_64_64_64</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_66</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_66_66_66_66</t>
+    <t xml:space="preserve">Unknown_66</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_67</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_67_67_67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_67_67_67</t>
-  </si>
-  <si>
     <t xml:space="preserve">Metschnikowia vanudenii</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_68</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_68_68_68_68</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_7</t>
   </si>
   <si>
-    <t xml:space="preserve">Saccharomycodaceae_7_7_7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hanseniaspora_7_7_7</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_72</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_72_72_72_72</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_73</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_73_73_73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_73_73_73</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_744</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_744_744_744_744</t>
+    <t xml:space="preserve">avinus</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_769</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_769_769_769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_769_769_769</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_78</t>
   </si>
   <si>
     <t xml:space="preserve">Ascoideales</t>
   </si>
   <si>
-    <t xml:space="preserve">Saccharomycopsidaceae_78_78_78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saccharomycopsis_78_78_78</t>
+    <t xml:space="preserve">Saccharomycopsidaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saccharomycopsis</t>
   </si>
   <si>
     <t xml:space="preserve">Saccharomycopsis crataegensis</t>
@@ -1052,10 +737,10 @@
     <t xml:space="preserve">Cluster_8</t>
   </si>
   <si>
-    <t xml:space="preserve">Saccotheciaceae_8_8_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aureobasidium_8_8_8</t>
+    <t xml:space="preserve">Saccotheciaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aureobasidium</t>
   </si>
   <si>
     <t xml:space="preserve">Aureobasidium pullulans</t>
@@ -1064,73 +749,34 @@
     <t xml:space="preserve">Cluster_81</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_81_81_81_81</t>
+    <t xml:space="preserve">Unknown_81</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_85</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_85_85_85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_85_85_85</t>
-  </si>
-  <si>
     <t xml:space="preserve">Metschnikowia gruessii</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_87</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_87_87_87_87</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_89</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_89_89_89_89</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_9</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_9_9_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_9_9_9</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_92</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_92_92_92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_92_92_92</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_95</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_95_95_95_95</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_96</t>
   </si>
   <si>
-    <t xml:space="preserve">Metschnikowiaceae_96_96_96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metschnikowia_96_96_96</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cladosporiaceae_98_98_98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cladosporium_98_98_98</t>
   </si>
 </sst>
 </file>
@@ -1658,18 +1304,18 @@
         <v>17</v>
       </c>
       <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s">
         <v>42</v>
-      </c>
-      <c r="G8" t="s">
-        <v>43</v>
-      </c>
-      <c r="H8" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
@@ -1684,18 +1330,18 @@
         <v>17</v>
       </c>
       <c r="F9" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="G9" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="H9" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
@@ -1710,36 +1356,36 @@
         <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="G10" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="H10" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="G11" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H11" t="s">
         <v>39</v>
@@ -1747,7 +1393,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
@@ -1762,10 +1408,10 @@
         <v>17</v>
       </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="G12" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="H12" t="s">
         <v>39</v>
@@ -1773,7 +1419,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B13" t="s">
         <v>9</v>
@@ -1788,18 +1434,18 @@
         <v>17</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="G13" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="H13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
@@ -1808,24 +1454,24 @@
         <v>10</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="F14" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G14" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H14" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B15" t="s">
         <v>9</v>
@@ -1837,13 +1483,13 @@
         <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F15" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G15" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="H15" t="s">
         <v>39</v>
@@ -1851,7 +1497,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
@@ -1866,36 +1512,36 @@
         <v>17</v>
       </c>
       <c r="F16" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="G16" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="H16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E17" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F17" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="G17" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="H17" t="s">
         <v>39</v>
@@ -1903,7 +1549,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="B18" t="s">
         <v>9</v>
@@ -1915,21 +1561,21 @@
         <v>22</v>
       </c>
       <c r="E18" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="F18" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="G18" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="H18" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="B19" t="s">
         <v>9</v>
@@ -1941,21 +1587,21 @@
         <v>22</v>
       </c>
       <c r="E19" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F19" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="G19" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="H19" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="B20" t="s">
         <v>9</v>
@@ -1970,10 +1616,10 @@
         <v>39</v>
       </c>
       <c r="F20" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="G20" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="H20" t="s">
         <v>39</v>
@@ -1981,7 +1627,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="B21" t="s">
         <v>9</v>
@@ -1993,13 +1639,13 @@
         <v>22</v>
       </c>
       <c r="E21" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F21" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="G21" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="H21" t="s">
         <v>39</v>
@@ -2007,33 +1653,33 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="B22" t="s">
         <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D22" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F22" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="G22" t="s">
-        <v>96</v>
+        <v>52</v>
       </c>
       <c r="H22" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="B23" t="s">
         <v>9</v>
@@ -2048,10 +1694,10 @@
         <v>17</v>
       </c>
       <c r="F23" t="s">
-        <v>99</v>
+        <v>18</v>
       </c>
       <c r="G23" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="H23" t="s">
         <v>39</v>
@@ -2059,7 +1705,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="B24" t="s">
         <v>9</v>
@@ -2071,21 +1717,21 @@
         <v>22</v>
       </c>
       <c r="E24" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F24" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="G24" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="H24" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
@@ -2097,13 +1743,13 @@
         <v>22</v>
       </c>
       <c r="E25" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="F25" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="G25" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="H25" t="s">
         <v>39</v>
@@ -2111,25 +1757,25 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D26" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E26" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F26" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="G26" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s">
         <v>39</v>
@@ -2137,7 +1783,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="B27" t="s">
         <v>9</v>
@@ -2152,10 +1798,10 @@
         <v>29</v>
       </c>
       <c r="F27" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="G27" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="H27" t="s">
         <v>39</v>
@@ -2163,25 +1809,25 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="B28" t="s">
         <v>9</v>
       </c>
       <c r="C28" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D28" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="E28" t="s">
         <v>39</v>
       </c>
       <c r="F28" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="G28" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="H28" t="s">
         <v>39</v>
@@ -2189,7 +1835,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="B29" t="s">
         <v>9</v>
@@ -2204,10 +1850,10 @@
         <v>39</v>
       </c>
       <c r="F29" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="G29" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="H29" t="s">
         <v>39</v>
@@ -2215,7 +1861,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="B30" t="s">
         <v>9</v>
@@ -2224,24 +1870,24 @@
         <v>10</v>
       </c>
       <c r="D30" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="E30" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="F30" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="G30" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="H30" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="B31" t="s">
         <v>9</v>
@@ -2250,16 +1896,16 @@
         <v>10</v>
       </c>
       <c r="D31" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E31" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="F31" t="s">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="G31" t="s">
-        <v>126</v>
+        <v>59</v>
       </c>
       <c r="H31" t="s">
         <v>39</v>
@@ -2267,7 +1913,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="B32" t="s">
         <v>9</v>
@@ -2282,18 +1928,18 @@
         <v>29</v>
       </c>
       <c r="F32" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="G32" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="H32" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="B33" t="s">
         <v>9</v>
@@ -2308,10 +1954,10 @@
         <v>12</v>
       </c>
       <c r="F33" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="G33" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -2319,7 +1965,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="B34" t="s">
         <v>9</v>
@@ -2334,18 +1980,18 @@
         <v>17</v>
       </c>
       <c r="F34" t="s">
-        <v>135</v>
+        <v>18</v>
       </c>
       <c r="G34" t="s">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="H34" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="B35" t="s">
         <v>9</v>
@@ -2354,16 +2000,16 @@
         <v>10</v>
       </c>
       <c r="D35" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="E35" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="F35" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="G35" t="s">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="H35" t="s">
         <v>39</v>
@@ -2371,51 +2017,51 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="B36" t="s">
         <v>9</v>
       </c>
       <c r="C36" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D36" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E36" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F36" t="s">
-        <v>143</v>
+        <v>51</v>
       </c>
       <c r="G36" t="s">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="H36" t="s">
-        <v>145</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>146</v>
+        <v>117</v>
       </c>
       <c r="B37" t="s">
         <v>9</v>
       </c>
       <c r="C37" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D37" t="s">
-        <v>147</v>
+        <v>118</v>
       </c>
       <c r="E37" t="s">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="F37" t="s">
-        <v>149</v>
+        <v>120</v>
       </c>
       <c r="G37" t="s">
-        <v>149</v>
+        <v>120</v>
       </c>
       <c r="H37" t="s">
         <v>39</v>
@@ -2423,7 +2069,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>150</v>
+        <v>121</v>
       </c>
       <c r="B38" t="s">
         <v>9</v>
@@ -2435,13 +2081,13 @@
         <v>22</v>
       </c>
       <c r="E38" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="F38" t="s">
-        <v>151</v>
+        <v>70</v>
       </c>
       <c r="G38" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="H38" t="s">
         <v>39</v>
@@ -2449,7 +2095,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="B39" t="s">
         <v>9</v>
@@ -2458,68 +2104,68 @@
         <v>10</v>
       </c>
       <c r="D39" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E39" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="F39" t="s">
-        <v>154</v>
+        <v>58</v>
       </c>
       <c r="G39" t="s">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="H39" t="s">
-        <v>156</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="B40" t="s">
         <v>9</v>
       </c>
       <c r="C40" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D40" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E40" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F40" t="s">
-        <v>158</v>
+        <v>51</v>
       </c>
       <c r="G40" t="s">
-        <v>159</v>
+        <v>52</v>
       </c>
       <c r="H40" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="B41" t="s">
-        <v>39</v>
+        <v>127</v>
       </c>
       <c r="C41" t="s">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="D41" t="s">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E41" t="s">
-        <v>39</v>
+        <v>130</v>
       </c>
       <c r="F41" t="s">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="G41" t="s">
-        <v>161</v>
+        <v>132</v>
       </c>
       <c r="H41" t="s">
         <v>39</v>
@@ -2527,7 +2173,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>162</v>
+        <v>133</v>
       </c>
       <c r="B42" t="s">
         <v>9</v>
@@ -2542,10 +2188,10 @@
         <v>17</v>
       </c>
       <c r="F42" t="s">
-        <v>163</v>
+        <v>18</v>
       </c>
       <c r="G42" t="s">
-        <v>164</v>
+        <v>19</v>
       </c>
       <c r="H42" t="s">
         <v>39</v>
@@ -2553,7 +2199,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="B43" t="s">
         <v>9</v>
@@ -2565,65 +2211,65 @@
         <v>22</v>
       </c>
       <c r="E43" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F43" t="s">
-        <v>166</v>
+        <v>63</v>
       </c>
       <c r="G43" t="s">
-        <v>167</v>
+        <v>64</v>
       </c>
       <c r="H43" t="s">
-        <v>168</v>
+        <v>135</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="B44" t="s">
         <v>9</v>
       </c>
       <c r="C44" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D44" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E44" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F44" t="s">
-        <v>170</v>
+        <v>51</v>
       </c>
       <c r="G44" t="s">
-        <v>171</v>
+        <v>52</v>
       </c>
       <c r="H44" t="s">
-        <v>172</v>
+        <v>137</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>173</v>
+        <v>138</v>
       </c>
       <c r="B45" t="s">
         <v>9</v>
       </c>
       <c r="C45" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D45" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E45" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F45" t="s">
-        <v>174</v>
+        <v>51</v>
       </c>
       <c r="G45" t="s">
-        <v>175</v>
+        <v>139</v>
       </c>
       <c r="H45" t="s">
         <v>39</v>
@@ -2631,7 +2277,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>176</v>
+        <v>140</v>
       </c>
       <c r="B46" t="s">
         <v>9</v>
@@ -2643,13 +2289,13 @@
         <v>22</v>
       </c>
       <c r="E46" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="F46" t="s">
-        <v>177</v>
+        <v>70</v>
       </c>
       <c r="G46" t="s">
-        <v>178</v>
+        <v>122</v>
       </c>
       <c r="H46" t="s">
         <v>39</v>
@@ -2657,7 +2303,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="B47" t="s">
         <v>9</v>
@@ -2669,13 +2315,13 @@
         <v>22</v>
       </c>
       <c r="E47" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F47" t="s">
-        <v>180</v>
+        <v>63</v>
       </c>
       <c r="G47" t="s">
-        <v>181</v>
+        <v>64</v>
       </c>
       <c r="H47" t="s">
         <v>39</v>
@@ -2683,7 +2329,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>182</v>
+        <v>142</v>
       </c>
       <c r="B48" t="s">
         <v>9</v>
@@ -2698,10 +2344,10 @@
         <v>17</v>
       </c>
       <c r="F48" t="s">
-        <v>183</v>
+        <v>18</v>
       </c>
       <c r="G48" t="s">
-        <v>184</v>
+        <v>19</v>
       </c>
       <c r="H48" t="s">
         <v>39</v>
@@ -2709,7 +2355,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>185</v>
+        <v>143</v>
       </c>
       <c r="B49" t="s">
         <v>9</v>
@@ -2724,10 +2370,10 @@
         <v>34</v>
       </c>
       <c r="F49" t="s">
-        <v>186</v>
+        <v>35</v>
       </c>
       <c r="G49" t="s">
-        <v>187</v>
+        <v>36</v>
       </c>
       <c r="H49" t="s">
         <v>37</v>
@@ -2735,7 +2381,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>188</v>
+        <v>144</v>
       </c>
       <c r="B50" t="s">
         <v>9</v>
@@ -2750,10 +2396,10 @@
         <v>17</v>
       </c>
       <c r="F50" t="s">
-        <v>189</v>
+        <v>18</v>
       </c>
       <c r="G50" t="s">
-        <v>190</v>
+        <v>19</v>
       </c>
       <c r="H50" t="s">
         <v>39</v>
@@ -2761,7 +2407,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>191</v>
+        <v>145</v>
       </c>
       <c r="B51" t="s">
         <v>9</v>
@@ -2776,36 +2422,36 @@
         <v>17</v>
       </c>
       <c r="F51" t="s">
-        <v>192</v>
+        <v>18</v>
       </c>
       <c r="G51" t="s">
-        <v>193</v>
+        <v>19</v>
       </c>
       <c r="H51" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
       <c r="B52" t="s">
         <v>9</v>
       </c>
       <c r="C52" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D52" t="s">
-        <v>195</v>
+        <v>147</v>
       </c>
       <c r="E52" t="s">
         <v>39</v>
       </c>
       <c r="F52" t="s">
-        <v>196</v>
+        <v>148</v>
       </c>
       <c r="G52" t="s">
-        <v>197</v>
+        <v>149</v>
       </c>
       <c r="H52" t="s">
         <v>39</v>
@@ -2813,33 +2459,33 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>198</v>
+        <v>150</v>
       </c>
       <c r="B53" t="s">
         <v>9</v>
       </c>
       <c r="C53" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D53" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="E53" t="s">
-        <v>199</v>
+        <v>151</v>
       </c>
       <c r="F53" t="s">
-        <v>200</v>
+        <v>152</v>
       </c>
       <c r="G53" t="s">
-        <v>201</v>
+        <v>153</v>
       </c>
       <c r="H53" t="s">
-        <v>202</v>
+        <v>154</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>203</v>
+        <v>155</v>
       </c>
       <c r="B54" t="s">
         <v>9</v>
@@ -2854,10 +2500,10 @@
         <v>29</v>
       </c>
       <c r="F54" t="s">
-        <v>204</v>
+        <v>30</v>
       </c>
       <c r="G54" t="s">
-        <v>205</v>
+        <v>31</v>
       </c>
       <c r="H54" t="s">
         <v>32</v>
@@ -2865,7 +2511,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>206</v>
+        <v>156</v>
       </c>
       <c r="B55" t="s">
         <v>9</v>
@@ -2877,21 +2523,21 @@
         <v>22</v>
       </c>
       <c r="E55" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F55" t="s">
-        <v>207</v>
+        <v>63</v>
       </c>
       <c r="G55" t="s">
-        <v>208</v>
+        <v>64</v>
       </c>
       <c r="H55" t="s">
-        <v>209</v>
+        <v>157</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>210</v>
+        <v>158</v>
       </c>
       <c r="B56" t="s">
         <v>9</v>
@@ -2906,18 +2552,18 @@
         <v>12</v>
       </c>
       <c r="F56" t="s">
-        <v>211</v>
+        <v>13</v>
       </c>
       <c r="G56" t="s">
-        <v>212</v>
+        <v>14</v>
       </c>
       <c r="H56" t="s">
-        <v>213</v>
+        <v>159</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>214</v>
+        <v>160</v>
       </c>
       <c r="B57" t="s">
         <v>9</v>
@@ -2926,50 +2572,50 @@
         <v>10</v>
       </c>
       <c r="D57" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="E57" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="F57" t="s">
-        <v>215</v>
+        <v>100</v>
       </c>
       <c r="G57" t="s">
-        <v>216</v>
+        <v>101</v>
       </c>
       <c r="H57" t="s">
-        <v>217</v>
+        <v>161</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>218</v>
+        <v>162</v>
       </c>
       <c r="B58" t="s">
         <v>9</v>
       </c>
       <c r="C58" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D58" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="E58" t="s">
-        <v>199</v>
+        <v>151</v>
       </c>
       <c r="F58" t="s">
-        <v>219</v>
+        <v>152</v>
       </c>
       <c r="G58" t="s">
-        <v>220</v>
+        <v>153</v>
       </c>
       <c r="H58" t="s">
-        <v>221</v>
+        <v>163</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>222</v>
+        <v>164</v>
       </c>
       <c r="B59" t="s">
         <v>9</v>
@@ -2984,36 +2630,36 @@
         <v>17</v>
       </c>
       <c r="F59" t="s">
-        <v>223</v>
+        <v>18</v>
       </c>
       <c r="G59" t="s">
-        <v>224</v>
+        <v>19</v>
       </c>
       <c r="H59" t="s">
-        <v>225</v>
+        <v>165</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>226</v>
+        <v>166</v>
       </c>
       <c r="B60" t="s">
-        <v>39</v>
+        <v>127</v>
       </c>
       <c r="C60" t="s">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="D60" t="s">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E60" t="s">
-        <v>39</v>
+        <v>130</v>
       </c>
       <c r="F60" t="s">
-        <v>227</v>
+        <v>131</v>
       </c>
       <c r="G60" t="s">
-        <v>227</v>
+        <v>132</v>
       </c>
       <c r="H60" t="s">
         <v>39</v>
@@ -3021,7 +2667,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>228</v>
+        <v>167</v>
       </c>
       <c r="B61" t="s">
         <v>9</v>
@@ -3036,18 +2682,18 @@
         <v>17</v>
       </c>
       <c r="F61" t="s">
-        <v>229</v>
+        <v>18</v>
       </c>
       <c r="G61" t="s">
-        <v>230</v>
+        <v>19</v>
       </c>
       <c r="H61" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>231</v>
+        <v>168</v>
       </c>
       <c r="B62" t="s">
         <v>9</v>
@@ -3062,18 +2708,18 @@
         <v>17</v>
       </c>
       <c r="F62" t="s">
-        <v>232</v>
+        <v>18</v>
       </c>
       <c r="G62" t="s">
-        <v>233</v>
+        <v>19</v>
       </c>
       <c r="H62" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>234</v>
+        <v>169</v>
       </c>
       <c r="B63" t="s">
         <v>9</v>
@@ -3088,10 +2734,10 @@
         <v>29</v>
       </c>
       <c r="F63" t="s">
-        <v>235</v>
+        <v>170</v>
       </c>
       <c r="G63" t="s">
-        <v>235</v>
+        <v>170</v>
       </c>
       <c r="H63" t="s">
         <v>39</v>
@@ -3099,25 +2745,25 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>236</v>
+        <v>171</v>
       </c>
       <c r="B64" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C64" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="D64" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E64" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F64" t="s">
-        <v>237</v>
+        <v>18</v>
       </c>
       <c r="G64" t="s">
-        <v>237</v>
+        <v>19</v>
       </c>
       <c r="H64" t="s">
         <v>39</v>
@@ -3125,7 +2771,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>238</v>
+        <v>172</v>
       </c>
       <c r="B65" t="s">
         <v>9</v>
@@ -3140,18 +2786,18 @@
         <v>34</v>
       </c>
       <c r="F65" t="s">
-        <v>239</v>
+        <v>35</v>
       </c>
       <c r="G65" t="s">
-        <v>240</v>
+        <v>36</v>
       </c>
       <c r="H65" t="s">
-        <v>241</v>
+        <v>173</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>242</v>
+        <v>174</v>
       </c>
       <c r="B66" t="s">
         <v>9</v>
@@ -3166,18 +2812,18 @@
         <v>17</v>
       </c>
       <c r="F66" t="s">
-        <v>243</v>
+        <v>18</v>
       </c>
       <c r="G66" t="s">
-        <v>244</v>
+        <v>19</v>
       </c>
       <c r="H66" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="B67" t="s">
         <v>9</v>
@@ -3192,44 +2838,44 @@
         <v>17</v>
       </c>
       <c r="F67" t="s">
-        <v>246</v>
+        <v>18</v>
       </c>
       <c r="G67" t="s">
-        <v>247</v>
+        <v>19</v>
       </c>
       <c r="H67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>248</v>
+        <v>176</v>
       </c>
       <c r="B68" t="s">
-        <v>39</v>
+        <v>127</v>
       </c>
       <c r="C68" t="s">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="D68" t="s">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E68" t="s">
-        <v>39</v>
+        <v>130</v>
       </c>
       <c r="F68" t="s">
-        <v>249</v>
+        <v>131</v>
       </c>
       <c r="G68" t="s">
-        <v>249</v>
+        <v>177</v>
       </c>
       <c r="H68" t="s">
-        <v>39</v>
+        <v>178</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>250</v>
+        <v>179</v>
       </c>
       <c r="B69" t="s">
         <v>9</v>
@@ -3244,10 +2890,10 @@
         <v>17</v>
       </c>
       <c r="F69" t="s">
-        <v>251</v>
+        <v>18</v>
       </c>
       <c r="G69" t="s">
-        <v>252</v>
+        <v>19</v>
       </c>
       <c r="H69" t="s">
         <v>20</v>
@@ -3255,7 +2901,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>253</v>
+        <v>180</v>
       </c>
       <c r="B70" t="s">
         <v>9</v>
@@ -3270,18 +2916,18 @@
         <v>17</v>
       </c>
       <c r="F70" t="s">
-        <v>254</v>
+        <v>18</v>
       </c>
       <c r="G70" t="s">
-        <v>255</v>
+        <v>19</v>
       </c>
       <c r="H70" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>256</v>
+        <v>181</v>
       </c>
       <c r="B71" t="s">
         <v>9</v>
@@ -3296,10 +2942,10 @@
         <v>29</v>
       </c>
       <c r="F71" t="s">
-        <v>257</v>
+        <v>30</v>
       </c>
       <c r="G71" t="s">
-        <v>258</v>
+        <v>31</v>
       </c>
       <c r="H71" t="s">
         <v>32</v>
@@ -3307,7 +2953,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>259</v>
+        <v>182</v>
       </c>
       <c r="B72" t="s">
         <v>9</v>
@@ -3322,10 +2968,10 @@
         <v>39</v>
       </c>
       <c r="F72" t="s">
-        <v>260</v>
+        <v>183</v>
       </c>
       <c r="G72" t="s">
-        <v>260</v>
+        <v>183</v>
       </c>
       <c r="H72" t="s">
         <v>39</v>
@@ -3333,7 +2979,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>261</v>
+        <v>184</v>
       </c>
       <c r="B73" t="s">
         <v>9</v>
@@ -3342,16 +2988,16 @@
         <v>10</v>
       </c>
       <c r="D73" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="E73" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="F73" t="s">
-        <v>262</v>
+        <v>185</v>
       </c>
       <c r="G73" t="s">
-        <v>263</v>
+        <v>186</v>
       </c>
       <c r="H73" t="s">
         <v>39</v>
@@ -3359,7 +3005,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>264</v>
+        <v>187</v>
       </c>
       <c r="B74" t="s">
         <v>9</v>
@@ -3368,16 +3014,16 @@
         <v>10</v>
       </c>
       <c r="D74" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="E74" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="F74" t="s">
-        <v>265</v>
+        <v>188</v>
       </c>
       <c r="G74" t="s">
-        <v>266</v>
+        <v>189</v>
       </c>
       <c r="H74" t="s">
         <v>39</v>
@@ -3385,59 +3031,59 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>267</v>
+        <v>190</v>
       </c>
       <c r="B75" t="s">
         <v>9</v>
       </c>
       <c r="C75" t="s">
-        <v>268</v>
+        <v>191</v>
       </c>
       <c r="D75" t="s">
-        <v>269</v>
+        <v>192</v>
       </c>
       <c r="E75" t="s">
-        <v>270</v>
+        <v>193</v>
       </c>
       <c r="F75" t="s">
-        <v>271</v>
+        <v>194</v>
       </c>
       <c r="G75" t="s">
-        <v>272</v>
+        <v>195</v>
       </c>
       <c r="H75" t="s">
-        <v>273</v>
+        <v>196</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>274</v>
+        <v>197</v>
       </c>
       <c r="B76" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C76" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="D76" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E76" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F76" t="s">
-        <v>275</v>
+        <v>18</v>
       </c>
       <c r="G76" t="s">
-        <v>275</v>
+        <v>19</v>
       </c>
       <c r="H76" t="s">
-        <v>39</v>
+        <v>198</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>276</v>
+        <v>199</v>
       </c>
       <c r="B77" t="s">
         <v>9</v>
@@ -3452,10 +3098,10 @@
         <v>29</v>
       </c>
       <c r="F77" t="s">
-        <v>277</v>
+        <v>30</v>
       </c>
       <c r="G77" t="s">
-        <v>278</v>
+        <v>31</v>
       </c>
       <c r="H77" t="s">
         <v>32</v>
@@ -3463,7 +3109,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>279</v>
+        <v>200</v>
       </c>
       <c r="B78" t="s">
         <v>9</v>
@@ -3478,44 +3124,44 @@
         <v>17</v>
       </c>
       <c r="F78" t="s">
-        <v>280</v>
+        <v>18</v>
       </c>
       <c r="G78" t="s">
-        <v>281</v>
+        <v>19</v>
       </c>
       <c r="H78" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>282</v>
+        <v>201</v>
       </c>
       <c r="B79" t="s">
         <v>9</v>
       </c>
       <c r="C79" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D79" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E79" t="s">
-        <v>283</v>
+        <v>202</v>
       </c>
       <c r="F79" t="s">
-        <v>284</v>
+        <v>203</v>
       </c>
       <c r="G79" t="s">
-        <v>285</v>
+        <v>204</v>
       </c>
       <c r="H79" t="s">
-        <v>286</v>
+        <v>205</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>287</v>
+        <v>206</v>
       </c>
       <c r="B80" t="s">
         <v>9</v>
@@ -3527,13 +3173,13 @@
         <v>22</v>
       </c>
       <c r="E80" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F80" t="s">
-        <v>288</v>
+        <v>63</v>
       </c>
       <c r="G80" t="s">
-        <v>289</v>
+        <v>64</v>
       </c>
       <c r="H80" t="s">
         <v>39</v>
@@ -3541,7 +3187,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>290</v>
+        <v>207</v>
       </c>
       <c r="B81" t="s">
         <v>9</v>
@@ -3556,10 +3202,10 @@
         <v>39</v>
       </c>
       <c r="F81" t="s">
-        <v>291</v>
+        <v>208</v>
       </c>
       <c r="G81" t="s">
-        <v>291</v>
+        <v>208</v>
       </c>
       <c r="H81" t="s">
         <v>39</v>
@@ -3567,7 +3213,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>292</v>
+        <v>209</v>
       </c>
       <c r="B82" t="s">
         <v>9</v>
@@ -3582,18 +3228,18 @@
         <v>17</v>
       </c>
       <c r="F82" t="s">
-        <v>293</v>
+        <v>18</v>
       </c>
       <c r="G82" t="s">
-        <v>294</v>
+        <v>19</v>
       </c>
       <c r="H82" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>295</v>
+        <v>210</v>
       </c>
       <c r="B83" t="s">
         <v>9</v>
@@ -3608,10 +3254,10 @@
         <v>39</v>
       </c>
       <c r="F83" t="s">
-        <v>296</v>
+        <v>211</v>
       </c>
       <c r="G83" t="s">
-        <v>296</v>
+        <v>211</v>
       </c>
       <c r="H83" t="s">
         <v>39</v>
@@ -3619,7 +3265,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>297</v>
+        <v>212</v>
       </c>
       <c r="B84" t="s">
         <v>9</v>
@@ -3634,18 +3280,18 @@
         <v>17</v>
       </c>
       <c r="F84" t="s">
-        <v>298</v>
+        <v>18</v>
       </c>
       <c r="G84" t="s">
-        <v>299</v>
+        <v>19</v>
       </c>
       <c r="H84" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>300</v>
+        <v>213</v>
       </c>
       <c r="B85" t="s">
         <v>9</v>
@@ -3660,10 +3306,10 @@
         <v>17</v>
       </c>
       <c r="F85" t="s">
-        <v>301</v>
+        <v>18</v>
       </c>
       <c r="G85" t="s">
-        <v>302</v>
+        <v>19</v>
       </c>
       <c r="H85" t="s">
         <v>39</v>
@@ -3671,51 +3317,51 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>303</v>
+        <v>214</v>
       </c>
       <c r="B86" t="s">
-        <v>39</v>
+        <v>127</v>
       </c>
       <c r="C86" t="s">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="D86" t="s">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E86" t="s">
-        <v>39</v>
+        <v>130</v>
       </c>
       <c r="F86" t="s">
-        <v>304</v>
+        <v>131</v>
       </c>
       <c r="G86" t="s">
-        <v>304</v>
+        <v>132</v>
       </c>
       <c r="H86" t="s">
-        <v>39</v>
+        <v>215</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>305</v>
+        <v>216</v>
       </c>
       <c r="B87" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C87" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="D87" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E87" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F87" t="s">
-        <v>306</v>
+        <v>18</v>
       </c>
       <c r="G87" t="s">
-        <v>306</v>
+        <v>19</v>
       </c>
       <c r="H87" t="s">
         <v>39</v>
@@ -3723,7 +3369,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>307</v>
+        <v>217</v>
       </c>
       <c r="B88" t="s">
         <v>9</v>
@@ -3738,18 +3384,18 @@
         <v>17</v>
       </c>
       <c r="F88" t="s">
-        <v>308</v>
+        <v>18</v>
       </c>
       <c r="G88" t="s">
-        <v>309</v>
+        <v>19</v>
       </c>
       <c r="H88" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>310</v>
+        <v>218</v>
       </c>
       <c r="B89" t="s">
         <v>9</v>
@@ -3758,16 +3404,16 @@
         <v>10</v>
       </c>
       <c r="D89" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="E89" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="F89" t="s">
-        <v>311</v>
+        <v>185</v>
       </c>
       <c r="G89" t="s">
-        <v>312</v>
+        <v>219</v>
       </c>
       <c r="H89" t="s">
         <v>39</v>
@@ -3775,7 +3421,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>313</v>
+        <v>220</v>
       </c>
       <c r="B90" t="s">
         <v>9</v>
@@ -3784,16 +3430,16 @@
         <v>10</v>
       </c>
       <c r="D90" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="E90" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="F90" t="s">
-        <v>314</v>
+        <v>221</v>
       </c>
       <c r="G90" t="s">
-        <v>315</v>
+        <v>222</v>
       </c>
       <c r="H90" t="s">
         <v>39</v>
@@ -3801,7 +3447,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>316</v>
+        <v>223</v>
       </c>
       <c r="B91" t="s">
         <v>9</v>
@@ -3816,18 +3462,18 @@
         <v>17</v>
       </c>
       <c r="F91" t="s">
-        <v>317</v>
+        <v>18</v>
       </c>
       <c r="G91" t="s">
-        <v>318</v>
+        <v>19</v>
       </c>
       <c r="H91" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>319</v>
+        <v>224</v>
       </c>
       <c r="B92" t="s">
         <v>9</v>
@@ -3842,10 +3488,10 @@
         <v>39</v>
       </c>
       <c r="F92" t="s">
-        <v>320</v>
+        <v>225</v>
       </c>
       <c r="G92" t="s">
-        <v>320</v>
+        <v>225</v>
       </c>
       <c r="H92" t="s">
         <v>39</v>
@@ -3853,7 +3499,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>321</v>
+        <v>226</v>
       </c>
       <c r="B93" t="s">
         <v>9</v>
@@ -3868,36 +3514,36 @@
         <v>17</v>
       </c>
       <c r="F93" t="s">
-        <v>322</v>
+        <v>18</v>
       </c>
       <c r="G93" t="s">
-        <v>323</v>
+        <v>19</v>
       </c>
       <c r="H93" t="s">
-        <v>324</v>
+        <v>227</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>325</v>
+        <v>228</v>
       </c>
       <c r="B94" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C94" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="D94" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E94" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F94" t="s">
-        <v>326</v>
+        <v>18</v>
       </c>
       <c r="G94" t="s">
-        <v>326</v>
+        <v>19</v>
       </c>
       <c r="H94" t="s">
         <v>39</v>
@@ -3905,7 +3551,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>327</v>
+        <v>229</v>
       </c>
       <c r="B95" t="s">
         <v>9</v>
@@ -3920,10 +3566,10 @@
         <v>29</v>
       </c>
       <c r="F95" t="s">
-        <v>328</v>
+        <v>90</v>
       </c>
       <c r="G95" t="s">
-        <v>329</v>
+        <v>91</v>
       </c>
       <c r="H95" t="s">
         <v>39</v>
@@ -3931,25 +3577,25 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>330</v>
+        <v>230</v>
       </c>
       <c r="B96" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C96" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="D96" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E96" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F96" t="s">
-        <v>331</v>
+        <v>18</v>
       </c>
       <c r="G96" t="s">
-        <v>331</v>
+        <v>19</v>
       </c>
       <c r="H96" t="s">
         <v>39</v>
@@ -3957,7 +3603,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>332</v>
+        <v>231</v>
       </c>
       <c r="B97" t="s">
         <v>9</v>
@@ -3972,44 +3618,44 @@
         <v>17</v>
       </c>
       <c r="F97" t="s">
-        <v>333</v>
+        <v>18</v>
       </c>
       <c r="G97" t="s">
-        <v>334</v>
+        <v>19</v>
       </c>
       <c r="H97" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>335</v>
+        <v>232</v>
       </c>
       <c r="B98" t="s">
-        <v>39</v>
+        <v>127</v>
       </c>
       <c r="C98" t="s">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="D98" t="s">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E98" t="s">
-        <v>39</v>
+        <v>130</v>
       </c>
       <c r="F98" t="s">
-        <v>336</v>
+        <v>131</v>
       </c>
       <c r="G98" t="s">
-        <v>336</v>
+        <v>177</v>
       </c>
       <c r="H98" t="s">
-        <v>39</v>
+        <v>233</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>337</v>
+        <v>234</v>
       </c>
       <c r="B99" t="s">
         <v>9</v>
@@ -4024,18 +3670,18 @@
         <v>17</v>
       </c>
       <c r="F99" t="s">
-        <v>338</v>
+        <v>18</v>
       </c>
       <c r="G99" t="s">
-        <v>339</v>
+        <v>19</v>
       </c>
       <c r="H99" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>340</v>
+        <v>235</v>
       </c>
       <c r="B100" t="s">
         <v>9</v>
@@ -4047,21 +3693,21 @@
         <v>28</v>
       </c>
       <c r="E100" t="s">
-        <v>341</v>
+        <v>236</v>
       </c>
       <c r="F100" t="s">
-        <v>342</v>
+        <v>237</v>
       </c>
       <c r="G100" t="s">
-        <v>343</v>
+        <v>238</v>
       </c>
       <c r="H100" t="s">
-        <v>344</v>
+        <v>239</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>345</v>
+        <v>240</v>
       </c>
       <c r="B101" t="s">
         <v>9</v>
@@ -4076,18 +3722,18 @@
         <v>23</v>
       </c>
       <c r="F101" t="s">
-        <v>346</v>
+        <v>241</v>
       </c>
       <c r="G101" t="s">
-        <v>347</v>
+        <v>242</v>
       </c>
       <c r="H101" t="s">
-        <v>348</v>
+        <v>243</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>349</v>
+        <v>244</v>
       </c>
       <c r="B102" t="s">
         <v>9</v>
@@ -4096,16 +3742,16 @@
         <v>10</v>
       </c>
       <c r="D102" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="E102" t="s">
         <v>39</v>
       </c>
       <c r="F102" t="s">
-        <v>350</v>
+        <v>245</v>
       </c>
       <c r="G102" t="s">
-        <v>350</v>
+        <v>245</v>
       </c>
       <c r="H102" t="s">
         <v>39</v>
@@ -4113,7 +3759,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>351</v>
+        <v>246</v>
       </c>
       <c r="B103" t="s">
         <v>9</v>
@@ -4128,36 +3774,36 @@
         <v>17</v>
       </c>
       <c r="F103" t="s">
-        <v>352</v>
+        <v>18</v>
       </c>
       <c r="G103" t="s">
-        <v>353</v>
+        <v>19</v>
       </c>
       <c r="H103" t="s">
-        <v>354</v>
+        <v>247</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>355</v>
+        <v>248</v>
       </c>
       <c r="B104" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C104" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="D104" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E104" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F104" t="s">
-        <v>356</v>
+        <v>18</v>
       </c>
       <c r="G104" t="s">
-        <v>356</v>
+        <v>19</v>
       </c>
       <c r="H104" t="s">
         <v>39</v>
@@ -4165,25 +3811,25 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>357</v>
+        <v>249</v>
       </c>
       <c r="B105" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C105" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="D105" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E105" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F105" t="s">
-        <v>358</v>
+        <v>18</v>
       </c>
       <c r="G105" t="s">
-        <v>358</v>
+        <v>19</v>
       </c>
       <c r="H105" t="s">
         <v>39</v>
@@ -4191,7 +3837,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>359</v>
+        <v>250</v>
       </c>
       <c r="B106" t="s">
         <v>9</v>
@@ -4206,18 +3852,18 @@
         <v>17</v>
       </c>
       <c r="F106" t="s">
-        <v>360</v>
+        <v>18</v>
       </c>
       <c r="G106" t="s">
-        <v>361</v>
+        <v>19</v>
       </c>
       <c r="H106" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>362</v>
+        <v>251</v>
       </c>
       <c r="B107" t="s">
         <v>9</v>
@@ -4232,44 +3878,44 @@
         <v>17</v>
       </c>
       <c r="F107" t="s">
-        <v>363</v>
+        <v>18</v>
       </c>
       <c r="G107" t="s">
-        <v>364</v>
+        <v>19</v>
       </c>
       <c r="H107" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>365</v>
+        <v>252</v>
       </c>
       <c r="B108" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C108" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="D108" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E108" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F108" t="s">
-        <v>366</v>
+        <v>18</v>
       </c>
       <c r="G108" t="s">
-        <v>366</v>
+        <v>19</v>
       </c>
       <c r="H108" t="s">
-        <v>39</v>
+        <v>198</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>367</v>
+        <v>253</v>
       </c>
       <c r="B109" t="s">
         <v>9</v>
@@ -4284,18 +3930,18 @@
         <v>17</v>
       </c>
       <c r="F109" t="s">
-        <v>368</v>
+        <v>18</v>
       </c>
       <c r="G109" t="s">
-        <v>369</v>
+        <v>19</v>
       </c>
       <c r="H109" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>370</v>
+        <v>254</v>
       </c>
       <c r="B110" t="s">
         <v>9</v>
@@ -4307,16 +3953,16 @@
         <v>22</v>
       </c>
       <c r="E110" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F110" t="s">
-        <v>371</v>
+        <v>63</v>
       </c>
       <c r="G110" t="s">
-        <v>372</v>
+        <v>64</v>
       </c>
       <c r="H110" t="s">
-        <v>209</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
